--- a/services/finale-workbook-intake/finale-export-christine.xlsx
+++ b/services/finale-workbook-intake/finale-export-christine.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\medical-aq-qa\services\finale-workbook-intake\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{777B2110-D57E-42F7-8AD9-4E023996BE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D97CF14-E7DF-4067-8A64-65F18C39A2D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4395" yWindow="2355" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OASIS Tracking Report" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Star Home Health Care Inc</t>
   </si>
@@ -67,40 +67,13 @@
     <t>Document: 30 Days Tracking</t>
   </si>
   <si>
-    <t>YELSH, WILLIAM</t>
-  </si>
-  <si>
-    <t>03/31/2026</t>
-  </si>
-  <si>
-    <t>03/31/2026 - 05/29/2026</t>
-  </si>
-  <si>
     <t>In Progress</t>
-  </si>
-  <si>
-    <t>01-SOC</t>
-  </si>
-  <si>
-    <t>Lara, Toni RN</t>
   </si>
   <si>
     <t>Medicare</t>
   </si>
   <si>
-    <t>PIERCE, RALPH</t>
-  </si>
-  <si>
-    <t>02/28/2026</t>
-  </si>
-  <si>
-    <t>02/28/2026 - 04/28/2026</t>
-  </si>
-  <si>
     <t>09-DC</t>
-  </si>
-  <si>
-    <t>Ivey, Karen PT</t>
   </si>
   <si>
     <t>HAUG, NANCY</t>
@@ -116,24 +89,6 @@
   </si>
   <si>
     <t>03/30/2026</t>
-  </si>
-  <si>
-    <t>Validated</t>
-  </si>
-  <si>
-    <t>YOUNG, CHRISTINE</t>
-  </si>
-  <si>
-    <t>02/27/2026</t>
-  </si>
-  <si>
-    <t>02/27/2026 - 04/27/2026</t>
-  </si>
-  <si>
-    <t>06-XFER</t>
-  </si>
-  <si>
-    <t>03/18/2026</t>
   </si>
   <si>
     <t>Printed on 03/31/2026</t>
@@ -328,6 +283,15 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -335,15 +299,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -364,9 +319,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -404,7 +359,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -510,7 +465,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -652,7 +607,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -661,7 +616,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BI125"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -674,7 +629,7 @@
     <col min="11" max="11" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -737,21 +692,21 @@
       <c r="BH1" s="1"/>
       <c r="BI1" s="1"/>
     </row>
-    <row r="2" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="14" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -803,21 +758,21 @@
       <c r="BG2" s="1"/>
       <c r="BH2" s="1"/>
     </row>
-    <row r="3" spans="1:61" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:61" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="16" t="s">
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -869,19 +824,19 @@
       <c r="BG3" s="1"/>
       <c r="BH3" s="1"/>
     </row>
-    <row r="4" spans="1:61" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:61" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -933,7 +888,7 @@
       <c r="BG4" s="1"/>
       <c r="BH4" s="1"/>
     </row>
-    <row r="5" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -996,7 +951,7 @@
       <c r="BH5" s="1"/>
       <c r="BI5" s="1"/>
     </row>
-    <row r="6" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="3" t="s">
         <v>5</v>
@@ -1076,19 +1031,19 @@
       <c r="BG6" s="1"/>
       <c r="BH6" s="1"/>
     </row>
-    <row r="7" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -1140,34 +1095,34 @@
       <c r="BG7" s="1"/>
       <c r="BH7" s="1"/>
     </row>
-    <row r="8" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="I8" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J8" s="6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -1220,35 +1175,17 @@
       <c r="BG8" s="1"/>
       <c r="BH8" s="1"/>
     </row>
-    <row r="9" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
-      <c r="B9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="9">
-        <v>30</v>
-      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="9"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -1300,35 +1237,8 @@
       <c r="BG9" s="1"/>
       <c r="BH9" s="1"/>
     </row>
-    <row r="10" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J10" s="6">
-        <v>29</v>
-      </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -1380,35 +1290,17 @@
       <c r="BG10" s="1"/>
       <c r="BH10" s="1"/>
     </row>
-    <row r="11" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J11" s="9">
-        <v>17</v>
-      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="9"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -1460,7 +1352,7 @@
       <c r="BG11" s="1"/>
       <c r="BH11" s="1"/>
     </row>
-    <row r="12" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="5"/>
       <c r="C12" s="2"/>
@@ -1522,7 +1414,7 @@
       <c r="BG12" s="1"/>
       <c r="BH12" s="1"/>
     </row>
-    <row r="13" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="7"/>
       <c r="C13" s="8"/>
@@ -1584,7 +1476,7 @@
       <c r="BG13" s="1"/>
       <c r="BH13" s="1"/>
     </row>
-    <row r="14" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="5"/>
       <c r="C14" s="2"/>
@@ -1646,7 +1538,7 @@
       <c r="BG14" s="1"/>
       <c r="BH14" s="1"/>
     </row>
-    <row r="15" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="7"/>
       <c r="C15" s="8"/>
@@ -1708,7 +1600,7 @@
       <c r="BG15" s="1"/>
       <c r="BH15" s="1"/>
     </row>
-    <row r="16" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="5"/>
       <c r="C16" s="2"/>
@@ -1770,7 +1662,7 @@
       <c r="BG16" s="1"/>
       <c r="BH16" s="1"/>
     </row>
-    <row r="17" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="7"/>
       <c r="C17" s="8"/>
@@ -1832,7 +1724,7 @@
       <c r="BG17" s="1"/>
       <c r="BH17" s="1"/>
     </row>
-    <row r="18" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="5"/>
       <c r="C18" s="2"/>
@@ -1894,7 +1786,7 @@
       <c r="BG18" s="1"/>
       <c r="BH18" s="1"/>
     </row>
-    <row r="19" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -1947,7 +1839,7 @@
       <c r="BG19" s="1"/>
       <c r="BH19" s="1"/>
     </row>
-    <row r="20" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="5"/>
       <c r="C20" s="2"/>
@@ -2009,7 +1901,7 @@
       <c r="BG20" s="1"/>
       <c r="BH20" s="1"/>
     </row>
-    <row r="21" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="7"/>
       <c r="C21" s="8"/>
@@ -2071,7 +1963,7 @@
       <c r="BG21" s="1"/>
       <c r="BH21" s="1"/>
     </row>
-    <row r="22" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="5"/>
       <c r="C22" s="2"/>
@@ -2133,7 +2025,7 @@
       <c r="BG22" s="1"/>
       <c r="BH22" s="1"/>
     </row>
-    <row r="23" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:61" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="10"/>
       <c r="C23" s="11"/>
@@ -2195,7 +2087,7 @@
       <c r="BG23" s="1"/>
       <c r="BH23" s="1"/>
     </row>
-    <row r="24" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -2258,21 +2150,21 @@
       <c r="BH24" s="1"/>
       <c r="BI24" s="1"/>
     </row>
-    <row r="25" spans="1:61" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:61" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="15" t="s">
-        <v>38</v>
+      <c r="B25" s="14" t="s">
+        <v>23</v>
       </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="18" t="s">
-        <v>39</v>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="15" t="s">
+        <v>24</v>
       </c>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="18"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -2324,7 +2216,7 @@
       <c r="BG25" s="1"/>
       <c r="BH25" s="1"/>
     </row>
-    <row r="26" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -2387,7 +2279,7 @@
       <c r="BH26" s="1"/>
       <c r="BI26" s="1"/>
     </row>
-    <row r="27" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -2450,7 +2342,7 @@
       <c r="BH27" s="1"/>
       <c r="BI27" s="1"/>
     </row>
-    <row r="28" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2513,7 +2405,7 @@
       <c r="BH28" s="1"/>
       <c r="BI28" s="1"/>
     </row>
-    <row r="29" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2576,7 +2468,7 @@
       <c r="BH29" s="1"/>
       <c r="BI29" s="1"/>
     </row>
-    <row r="30" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2639,7 +2531,7 @@
       <c r="BH30" s="1"/>
       <c r="BI30" s="1"/>
     </row>
-    <row r="31" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2702,7 +2594,7 @@
       <c r="BH31" s="1"/>
       <c r="BI31" s="1"/>
     </row>
-    <row r="32" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2765,7 +2657,7 @@
       <c r="BH32" s="1"/>
       <c r="BI32" s="1"/>
     </row>
-    <row r="33" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -2828,7 +2720,7 @@
       <c r="BH33" s="1"/>
       <c r="BI33" s="1"/>
     </row>
-    <row r="34" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -2891,7 +2783,7 @@
       <c r="BH34" s="1"/>
       <c r="BI34" s="1"/>
     </row>
-    <row r="35" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -2954,7 +2846,7 @@
       <c r="BH35" s="1"/>
       <c r="BI35" s="1"/>
     </row>
-    <row r="36" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -3017,7 +2909,7 @@
       <c r="BH36" s="1"/>
       <c r="BI36" s="1"/>
     </row>
-    <row r="37" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -3080,7 +2972,7 @@
       <c r="BH37" s="1"/>
       <c r="BI37" s="1"/>
     </row>
-    <row r="38" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -3143,7 +3035,7 @@
       <c r="BH38" s="1"/>
       <c r="BI38" s="1"/>
     </row>
-    <row r="39" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -3206,7 +3098,7 @@
       <c r="BH39" s="1"/>
       <c r="BI39" s="1"/>
     </row>
-    <row r="40" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -3269,7 +3161,7 @@
       <c r="BH40" s="1"/>
       <c r="BI40" s="1"/>
     </row>
-    <row r="41" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -3332,7 +3224,7 @@
       <c r="BH41" s="1"/>
       <c r="BI41" s="1"/>
     </row>
-    <row r="42" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -3395,7 +3287,7 @@
       <c r="BH42" s="1"/>
       <c r="BI42" s="1"/>
     </row>
-    <row r="43" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -3458,7 +3350,7 @@
       <c r="BH43" s="1"/>
       <c r="BI43" s="1"/>
     </row>
-    <row r="44" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -3521,7 +3413,7 @@
       <c r="BH44" s="1"/>
       <c r="BI44" s="1"/>
     </row>
-    <row r="45" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -3584,7 +3476,7 @@
       <c r="BH45" s="1"/>
       <c r="BI45" s="1"/>
     </row>
-    <row r="46" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -3647,7 +3539,7 @@
       <c r="BH46" s="1"/>
       <c r="BI46" s="1"/>
     </row>
-    <row r="47" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -3710,7 +3602,7 @@
       <c r="BH47" s="1"/>
       <c r="BI47" s="1"/>
     </row>
-    <row r="48" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -3773,7 +3665,7 @@
       <c r="BH48" s="1"/>
       <c r="BI48" s="1"/>
     </row>
-    <row r="49" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -3836,7 +3728,7 @@
       <c r="BH49" s="1"/>
       <c r="BI49" s="1"/>
     </row>
-    <row r="50" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -3899,7 +3791,7 @@
       <c r="BH50" s="1"/>
       <c r="BI50" s="1"/>
     </row>
-    <row r="51" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -3962,7 +3854,7 @@
       <c r="BH51" s="1"/>
       <c r="BI51" s="1"/>
     </row>
-    <row r="52" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -4025,7 +3917,7 @@
       <c r="BH52" s="1"/>
       <c r="BI52" s="1"/>
     </row>
-    <row r="53" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -4088,7 +3980,7 @@
       <c r="BH53" s="1"/>
       <c r="BI53" s="1"/>
     </row>
-    <row r="54" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -4151,7 +4043,7 @@
       <c r="BH54" s="1"/>
       <c r="BI54" s="1"/>
     </row>
-    <row r="55" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -4214,7 +4106,7 @@
       <c r="BH55" s="1"/>
       <c r="BI55" s="1"/>
     </row>
-    <row r="56" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -4277,7 +4169,7 @@
       <c r="BH56" s="1"/>
       <c r="BI56" s="1"/>
     </row>
-    <row r="57" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -4340,7 +4232,7 @@
       <c r="BH57" s="1"/>
       <c r="BI57" s="1"/>
     </row>
-    <row r="58" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -4403,7 +4295,7 @@
       <c r="BH58" s="1"/>
       <c r="BI58" s="1"/>
     </row>
-    <row r="59" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -4466,7 +4358,7 @@
       <c r="BH59" s="1"/>
       <c r="BI59" s="1"/>
     </row>
-    <row r="60" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -4529,7 +4421,7 @@
       <c r="BH60" s="1"/>
       <c r="BI60" s="1"/>
     </row>
-    <row r="61" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -4592,7 +4484,7 @@
       <c r="BH61" s="1"/>
       <c r="BI61" s="1"/>
     </row>
-    <row r="62" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -4655,7 +4547,7 @@
       <c r="BH62" s="1"/>
       <c r="BI62" s="1"/>
     </row>
-    <row r="63" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -4718,7 +4610,7 @@
       <c r="BH63" s="1"/>
       <c r="BI63" s="1"/>
     </row>
-    <row r="64" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -4781,7 +4673,7 @@
       <c r="BH64" s="1"/>
       <c r="BI64" s="1"/>
     </row>
-    <row r="65" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -4844,7 +4736,7 @@
       <c r="BH65" s="1"/>
       <c r="BI65" s="1"/>
     </row>
-    <row r="66" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -4907,7 +4799,7 @@
       <c r="BH66" s="1"/>
       <c r="BI66" s="1"/>
     </row>
-    <row r="67" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -4970,7 +4862,7 @@
       <c r="BH67" s="1"/>
       <c r="BI67" s="1"/>
     </row>
-    <row r="68" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -5033,7 +4925,7 @@
       <c r="BH68" s="1"/>
       <c r="BI68" s="1"/>
     </row>
-    <row r="69" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -5096,7 +4988,7 @@
       <c r="BH69" s="1"/>
       <c r="BI69" s="1"/>
     </row>
-    <row r="70" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -5159,7 +5051,7 @@
       <c r="BH70" s="1"/>
       <c r="BI70" s="1"/>
     </row>
-    <row r="71" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -5222,7 +5114,7 @@
       <c r="BH71" s="1"/>
       <c r="BI71" s="1"/>
     </row>
-    <row r="72" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -5285,7 +5177,7 @@
       <c r="BH72" s="1"/>
       <c r="BI72" s="1"/>
     </row>
-    <row r="73" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -5348,7 +5240,7 @@
       <c r="BH73" s="1"/>
       <c r="BI73" s="1"/>
     </row>
-    <row r="74" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -5411,7 +5303,7 @@
       <c r="BH74" s="1"/>
       <c r="BI74" s="1"/>
     </row>
-    <row r="75" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -5474,7 +5366,7 @@
       <c r="BH75" s="1"/>
       <c r="BI75" s="1"/>
     </row>
-    <row r="76" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -5537,7 +5429,7 @@
       <c r="BH76" s="1"/>
       <c r="BI76" s="1"/>
     </row>
-    <row r="77" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -5600,7 +5492,7 @@
       <c r="BH77" s="1"/>
       <c r="BI77" s="1"/>
     </row>
-    <row r="78" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -5663,7 +5555,7 @@
       <c r="BH78" s="1"/>
       <c r="BI78" s="1"/>
     </row>
-    <row r="79" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -5726,7 +5618,7 @@
       <c r="BH79" s="1"/>
       <c r="BI79" s="1"/>
     </row>
-    <row r="80" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -5789,7 +5681,7 @@
       <c r="BH80" s="1"/>
       <c r="BI80" s="1"/>
     </row>
-    <row r="81" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -5852,7 +5744,7 @@
       <c r="BH81" s="1"/>
       <c r="BI81" s="1"/>
     </row>
-    <row r="82" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -5915,7 +5807,7 @@
       <c r="BH82" s="1"/>
       <c r="BI82" s="1"/>
     </row>
-    <row r="83" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -5978,7 +5870,7 @@
       <c r="BH83" s="1"/>
       <c r="BI83" s="1"/>
     </row>
-    <row r="84" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -6041,7 +5933,7 @@
       <c r="BH84" s="1"/>
       <c r="BI84" s="1"/>
     </row>
-    <row r="85" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -6104,7 +5996,7 @@
       <c r="BH85" s="1"/>
       <c r="BI85" s="1"/>
     </row>
-    <row r="86" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -6167,7 +6059,7 @@
       <c r="BH86" s="1"/>
       <c r="BI86" s="1"/>
     </row>
-    <row r="87" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -6230,7 +6122,7 @@
       <c r="BH87" s="1"/>
       <c r="BI87" s="1"/>
     </row>
-    <row r="88" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -6293,7 +6185,7 @@
       <c r="BH88" s="1"/>
       <c r="BI88" s="1"/>
     </row>
-    <row r="89" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -6356,7 +6248,7 @@
       <c r="BH89" s="1"/>
       <c r="BI89" s="1"/>
     </row>
-    <row r="90" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -6419,7 +6311,7 @@
       <c r="BH90" s="1"/>
       <c r="BI90" s="1"/>
     </row>
-    <row r="91" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -6482,7 +6374,7 @@
       <c r="BH91" s="1"/>
       <c r="BI91" s="1"/>
     </row>
-    <row r="92" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -6545,7 +6437,7 @@
       <c r="BH92" s="1"/>
       <c r="BI92" s="1"/>
     </row>
-    <row r="93" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -6608,7 +6500,7 @@
       <c r="BH93" s="1"/>
       <c r="BI93" s="1"/>
     </row>
-    <row r="94" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -6671,7 +6563,7 @@
       <c r="BH94" s="1"/>
       <c r="BI94" s="1"/>
     </row>
-    <row r="95" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -6734,7 +6626,7 @@
       <c r="BH95" s="1"/>
       <c r="BI95" s="1"/>
     </row>
-    <row r="96" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -6797,7 +6689,7 @@
       <c r="BH96" s="1"/>
       <c r="BI96" s="1"/>
     </row>
-    <row r="97" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -6860,7 +6752,7 @@
       <c r="BH97" s="1"/>
       <c r="BI97" s="1"/>
     </row>
-    <row r="98" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -6923,7 +6815,7 @@
       <c r="BH98" s="1"/>
       <c r="BI98" s="1"/>
     </row>
-    <row r="99" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -6986,7 +6878,7 @@
       <c r="BH99" s="1"/>
       <c r="BI99" s="1"/>
     </row>
-    <row r="100" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -7049,7 +6941,7 @@
       <c r="BH100" s="1"/>
       <c r="BI100" s="1"/>
     </row>
-    <row r="101" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -7112,7 +7004,7 @@
       <c r="BH101" s="1"/>
       <c r="BI101" s="1"/>
     </row>
-    <row r="102" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -7175,7 +7067,7 @@
       <c r="BH102" s="1"/>
       <c r="BI102" s="1"/>
     </row>
-    <row r="103" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -7238,7 +7130,7 @@
       <c r="BH103" s="1"/>
       <c r="BI103" s="1"/>
     </row>
-    <row r="104" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -7301,7 +7193,7 @@
       <c r="BH104" s="1"/>
       <c r="BI104" s="1"/>
     </row>
-    <row r="105" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -7364,7 +7256,7 @@
       <c r="BH105" s="1"/>
       <c r="BI105" s="1"/>
     </row>
-    <row r="106" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -7427,7 +7319,7 @@
       <c r="BH106" s="1"/>
       <c r="BI106" s="1"/>
     </row>
-    <row r="107" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -7490,7 +7382,7 @@
       <c r="BH107" s="1"/>
       <c r="BI107" s="1"/>
     </row>
-    <row r="108" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -7553,7 +7445,7 @@
       <c r="BH108" s="1"/>
       <c r="BI108" s="1"/>
     </row>
-    <row r="109" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -7616,7 +7508,7 @@
       <c r="BH109" s="1"/>
       <c r="BI109" s="1"/>
     </row>
-    <row r="110" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -7679,7 +7571,7 @@
       <c r="BH110" s="1"/>
       <c r="BI110" s="1"/>
     </row>
-    <row r="111" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -7742,7 +7634,7 @@
       <c r="BH111" s="1"/>
       <c r="BI111" s="1"/>
     </row>
-    <row r="112" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -7805,7 +7697,7 @@
       <c r="BH112" s="1"/>
       <c r="BI112" s="1"/>
     </row>
-    <row r="113" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -7868,7 +7760,7 @@
       <c r="BH113" s="1"/>
       <c r="BI113" s="1"/>
     </row>
-    <row r="114" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -7931,7 +7823,7 @@
       <c r="BH114" s="1"/>
       <c r="BI114" s="1"/>
     </row>
-    <row r="115" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -7994,7 +7886,7 @@
       <c r="BH115" s="1"/>
       <c r="BI115" s="1"/>
     </row>
-    <row r="116" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -8057,7 +7949,7 @@
       <c r="BH116" s="1"/>
       <c r="BI116" s="1"/>
     </row>
-    <row r="117" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -8120,7 +8012,7 @@
       <c r="BH117" s="1"/>
       <c r="BI117" s="1"/>
     </row>
-    <row r="118" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -8183,7 +8075,7 @@
       <c r="BH118" s="1"/>
       <c r="BI118" s="1"/>
     </row>
-    <row r="119" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -8246,7 +8138,7 @@
       <c r="BH119" s="1"/>
       <c r="BI119" s="1"/>
     </row>
-    <row r="120" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -8309,7 +8201,7 @@
       <c r="BH120" s="1"/>
       <c r="BI120" s="1"/>
     </row>
-    <row r="121" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -8372,7 +8264,7 @@
       <c r="BH121" s="1"/>
       <c r="BI121" s="1"/>
     </row>
-    <row r="122" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -8435,7 +8327,7 @@
       <c r="BH122" s="1"/>
       <c r="BI122" s="1"/>
     </row>
-    <row r="123" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -8498,7 +8390,7 @@
       <c r="BH123" s="1"/>
       <c r="BI123" s="1"/>
     </row>
-    <row r="124" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -8561,7 +8453,7 @@
       <c r="BH124" s="1"/>
       <c r="BI124" s="1"/>
     </row>
-    <row r="125" spans="1:61" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
